--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_35.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_35.xlsx
@@ -471,132 +471,132 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4837</v>
+        <v>13545</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sra. Luna Caldeira</t>
+          <t>Sr. Davi Costela</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45082</v>
+        <v>45087</v>
       </c>
       <c r="G2" t="n">
-        <v>6871.51</v>
+        <v>11416.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67767</v>
+        <v>69812</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alana Barbosa</t>
+          <t>Laís Fogaça</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45080</v>
+        <v>45079</v>
       </c>
       <c r="G3" t="n">
-        <v>4374.69</v>
+        <v>10421.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91988</v>
+        <v>29260</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dr. Paulo Castro</t>
+          <t>Nicole Jesus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45082</v>
+        <v>45094</v>
       </c>
       <c r="G4" t="n">
-        <v>9521.42</v>
+        <v>6162.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12832</v>
+        <v>86165</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kamilly da Luz</t>
+          <t>Bárbara Barros</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45088</v>
+        <v>45079</v>
       </c>
       <c r="G5" t="n">
-        <v>6745.04</v>
+        <v>7622.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7663</v>
+        <v>85424</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maria Fernanda da Mata</t>
+          <t>Luiz Miguel Ramos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45096</v>
+        <v>45091</v>
       </c>
       <c r="G6" t="n">
-        <v>5563.91</v>
+        <v>3253.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25435</v>
+        <v>39734</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alana Moraes</t>
+          <t>Dra. Stella Souza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45104</v>
+        <v>45080</v>
       </c>
       <c r="G7" t="n">
-        <v>7112.65</v>
+        <v>2542.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54498</v>
+        <v>64496</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Erick Novaes</t>
+          <t>Yasmin Melo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,27 +663,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45084</v>
+        <v>45099</v>
       </c>
       <c r="G8" t="n">
-        <v>5979.87</v>
+        <v>9534</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60944</v>
+        <v>77256</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marcela Campos</t>
+          <t>João Guilherme Moreira</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -692,56 +692,56 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45102</v>
+        <v>45101</v>
       </c>
       <c r="G9" t="n">
-        <v>9522.889999999999</v>
+        <v>5127.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13925</v>
+        <v>79471</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bruno Novaes</t>
+          <t>Maria Fernanda Costela</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45098</v>
+        <v>45079</v>
       </c>
       <c r="G10" t="n">
-        <v>10802.35</v>
+        <v>8237.940000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>24737</v>
+        <v>27912</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lívia Fernandes</t>
+          <t>Dra. Juliana Cavalcanti</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45087</v>
+        <v>45080</v>
       </c>
       <c r="G11" t="n">
-        <v>8193.15</v>
+        <v>7003.89</v>
       </c>
     </row>
   </sheetData>
